--- a/software/data_base/BD.xlsx
+++ b/software/data_base/BD.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31511B1E-D1B9-4580-8A58-CE51DF4C67C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64C628BE-CDA0-490D-BCDA-F4CE5D2B5D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:13">

--- a/software/data_base/BD.xlsx
+++ b/software/data_base/BD.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64C628BE-CDA0-490D-BCDA-F4CE5D2B5D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{226983AC-5BED-486D-8EAF-5E32545E1B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="221">
   <si>
     <t>ID</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Syg</t>
   </si>
   <si>
+    <t>TypeR</t>
+  </si>
+  <si>
     <t>tar_A</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>U</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>AN</t>
   </si>
   <si>
@@ -130,6 +136,9 @@
     <t>A</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>PSSMAXT1</t>
   </si>
   <si>
@@ -142,6 +151,9 @@
     <t>S</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>PSSMAXT2</t>
   </si>
   <si>
@@ -190,337 +202,340 @@
     <t>макс сила тока A контура 5V</t>
   </si>
   <si>
+    <t>PSSMAXA33</t>
+  </si>
+  <si>
+    <t>макс сила тока A контура 3.3V</t>
+  </si>
+  <si>
+    <t>PSST1</t>
+  </si>
+  <si>
+    <t>температура контура 1</t>
+  </si>
+  <si>
+    <t>PSST2</t>
+  </si>
+  <si>
+    <t>температура контура 2</t>
+  </si>
+  <si>
+    <t>PSSA</t>
+  </si>
+  <si>
+    <t>сила тока A батареи</t>
+  </si>
+  <si>
+    <t>PSSW</t>
+  </si>
+  <si>
+    <t>мощность W батареи</t>
+  </si>
+  <si>
+    <t>PSSV</t>
+  </si>
+  <si>
+    <t>напряжение V батареи</t>
+  </si>
+  <si>
+    <t>PSSC</t>
+  </si>
+  <si>
+    <t>заряд C батареи</t>
+  </si>
+  <si>
+    <t>PSSA12</t>
+  </si>
+  <si>
+    <t>сила тока контура 12V</t>
+  </si>
+  <si>
+    <t>PSSV12</t>
+  </si>
+  <si>
+    <t>напряжение контура 12V</t>
+  </si>
+  <si>
+    <t>PSSA6</t>
+  </si>
+  <si>
+    <t>сила тока контура 6V</t>
+  </si>
+  <si>
+    <t>PSSV6</t>
+  </si>
+  <si>
+    <t>напряжение контура 6V</t>
+  </si>
+  <si>
+    <t>PSSA5</t>
+  </si>
+  <si>
+    <t>сила тока контура 5V</t>
+  </si>
+  <si>
+    <t>PSSV5</t>
+  </si>
+  <si>
+    <t>напряжение контура 5V</t>
+  </si>
+  <si>
+    <t>PSSA33</t>
+  </si>
+  <si>
+    <t>сила тока контура 3.3V</t>
+  </si>
+  <si>
+    <t>PSSV33</t>
+  </si>
+  <si>
+    <t>напряжение контура 3.3V</t>
+  </si>
+  <si>
+    <t>TCSPWR</t>
+  </si>
+  <si>
+    <t>TCS вкл/выкл</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>TCSPSS</t>
+  </si>
+  <si>
+    <t>опрос PSS</t>
+  </si>
+  <si>
+    <t>TCSTMS</t>
+  </si>
+  <si>
+    <t>опрос TMS</t>
+  </si>
+  <si>
+    <t>TCSMNS</t>
+  </si>
+  <si>
+    <t>опрос MNS</t>
+  </si>
+  <si>
+    <t>TCSLS</t>
+  </si>
+  <si>
+    <t>опрос LS</t>
+  </si>
+  <si>
+    <t>TCSCLOCK</t>
+  </si>
+  <si>
+    <t>счетчик TCS</t>
+  </si>
+  <si>
+    <t>TCSFRQ</t>
+  </si>
+  <si>
+    <t>скорость опроса систем</t>
+  </si>
+  <si>
+    <t>TCST</t>
+  </si>
+  <si>
+    <t>температура TCS</t>
+  </si>
+  <si>
+    <t>TMSPWR</t>
+  </si>
+  <si>
+    <t>TMS вкл/выкл</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>TMSCLOCK</t>
+  </si>
+  <si>
+    <t>счетчик TMS</t>
+  </si>
+  <si>
+    <t>TMSPWRFAN1</t>
+  </si>
+  <si>
+    <t>питание кулера 1</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>TMSPWRFAN2</t>
+  </si>
+  <si>
+    <t>питание кулера 2</t>
+  </si>
+  <si>
+    <t>TMSPWRFAN3</t>
+  </si>
+  <si>
+    <t>питание кулера 3</t>
+  </si>
+  <si>
+    <t>TMSPWRFAN4</t>
+  </si>
+  <si>
+    <t>питание кулера 4</t>
+  </si>
+  <si>
+    <t>TMST</t>
+  </si>
+  <si>
+    <t>температура TMS</t>
+  </si>
+  <si>
+    <t>MNSPWR</t>
+  </si>
+  <si>
+    <t>MNS</t>
+  </si>
+  <si>
+    <t>MNSCLOCK</t>
+  </si>
+  <si>
+    <t>счетчик MNS</t>
+  </si>
+  <si>
+    <t>MNST</t>
+  </si>
+  <si>
+    <t>температура MNS</t>
+  </si>
+  <si>
+    <t>LSPWR</t>
+  </si>
+  <si>
+    <t>LS вкл/выкл</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>LSCLOCK</t>
+  </si>
+  <si>
+    <t>счетчик LS</t>
+  </si>
+  <si>
+    <t>LST</t>
+  </si>
+  <si>
+    <t>температура LS</t>
+  </si>
+  <si>
+    <t>CPSSINIT</t>
+  </si>
+  <si>
+    <t>запуск PSS системы</t>
+  </si>
+  <si>
+    <t>CPSSPWRON</t>
+  </si>
+  <si>
+    <t>PSS вкл</t>
+  </si>
+  <si>
+    <t>CPSSPWROFF</t>
+  </si>
+  <si>
+    <t>PSS выкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR12ON</t>
+  </si>
+  <si>
+    <t>питание контура 12V вкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR12OFF</t>
+  </si>
+  <si>
+    <t>питание контура 12V выкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR6ON</t>
+  </si>
+  <si>
+    <t>питание контура 6V вкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR6OFF</t>
+  </si>
+  <si>
+    <t>питание контура 6V выкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR5ON</t>
+  </si>
+  <si>
+    <t>питание контура 5V вкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR5OFF</t>
+  </si>
+  <si>
+    <t>питание контура 5V выкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR33ON</t>
+  </si>
+  <si>
+    <t>питание контура 3.3V вкл</t>
+  </si>
+  <si>
+    <t>CPSSPWR33OFF</t>
+  </si>
+  <si>
+    <t>питание контура 3.3V выкл</t>
+  </si>
+  <si>
+    <t>CPSSECOON</t>
+  </si>
+  <si>
+    <t>режим экономии энергии вкл</t>
+  </si>
+  <si>
+    <t>CPSSECOOFF</t>
+  </si>
+  <si>
+    <t>режим экономии энергии выкл</t>
+  </si>
+  <si>
+    <t>CPSSMAXT1</t>
+  </si>
+  <si>
+    <t>CPSSMAXT2</t>
+  </si>
+  <si>
+    <t>CPSSMAXA</t>
+  </si>
+  <si>
+    <t>CPSSMAXW</t>
+  </si>
+  <si>
+    <t>CPSSMINC</t>
+  </si>
+  <si>
+    <t>CPSSMINV</t>
+  </si>
+  <si>
+    <t>CPSSMAXA12</t>
+  </si>
+  <si>
+    <t>CPSSMAXA6</t>
+  </si>
+  <si>
+    <t>CPSSMAXA5</t>
+  </si>
+  <si>
     <t>CPSSMAXA33</t>
-  </si>
-  <si>
-    <t>макс сила тока A контура 3.3V</t>
-  </si>
-  <si>
-    <t>PSST1</t>
-  </si>
-  <si>
-    <t>температура контура 1</t>
-  </si>
-  <si>
-    <t>PSST2</t>
-  </si>
-  <si>
-    <t>температура контура 2</t>
-  </si>
-  <si>
-    <t>PSSA</t>
-  </si>
-  <si>
-    <t>сила тока A батареи</t>
-  </si>
-  <si>
-    <t>PSSW</t>
-  </si>
-  <si>
-    <t>мощность W батареи</t>
-  </si>
-  <si>
-    <t>PSSV</t>
-  </si>
-  <si>
-    <t>напряжение V батареи</t>
-  </si>
-  <si>
-    <t>PSSC</t>
-  </si>
-  <si>
-    <t>заряд C батареи</t>
-  </si>
-  <si>
-    <t>PSSA12</t>
-  </si>
-  <si>
-    <t>сила тока контура 12V</t>
-  </si>
-  <si>
-    <t>PSSV12</t>
-  </si>
-  <si>
-    <t>напряжение контура 12V</t>
-  </si>
-  <si>
-    <t>PSSA6</t>
-  </si>
-  <si>
-    <t>сила тока контура 6V</t>
-  </si>
-  <si>
-    <t>PSSV6</t>
-  </si>
-  <si>
-    <t>напряжение контура 6V</t>
-  </si>
-  <si>
-    <t>PSSA5</t>
-  </si>
-  <si>
-    <t>сила тока контура 5V</t>
-  </si>
-  <si>
-    <t>PSSV5</t>
-  </si>
-  <si>
-    <t>напряжение контура 5V</t>
-  </si>
-  <si>
-    <t>PSSA33</t>
-  </si>
-  <si>
-    <t>сила тока контура 3.3V</t>
-  </si>
-  <si>
-    <t>PSSV33</t>
-  </si>
-  <si>
-    <t>напряжение контура 3.3V</t>
-  </si>
-  <si>
-    <t>TCSPWR</t>
-  </si>
-  <si>
-    <t>TCS вкл/выкл</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>TCSPSS</t>
-  </si>
-  <si>
-    <t>опрос PSS</t>
-  </si>
-  <si>
-    <t>TCSTMS</t>
-  </si>
-  <si>
-    <t>опрос TMS</t>
-  </si>
-  <si>
-    <t>TCSMNS</t>
-  </si>
-  <si>
-    <t>опрос MNS</t>
-  </si>
-  <si>
-    <t>TCSLS</t>
-  </si>
-  <si>
-    <t>опрос LS</t>
-  </si>
-  <si>
-    <t>TCSCLOCK</t>
-  </si>
-  <si>
-    <t>счетчик TCS</t>
-  </si>
-  <si>
-    <t>TCSFRQ</t>
-  </si>
-  <si>
-    <t>скорость опроса систем</t>
-  </si>
-  <si>
-    <t>TCST</t>
-  </si>
-  <si>
-    <t>температура TCS</t>
-  </si>
-  <si>
-    <t>TMSPWR</t>
-  </si>
-  <si>
-    <t>TMS вкл/выкл</t>
-  </si>
-  <si>
-    <t>TMS</t>
-  </si>
-  <si>
-    <t>TMSCLOCK</t>
-  </si>
-  <si>
-    <t>счетчик TMS</t>
-  </si>
-  <si>
-    <t>TMSPWRFAN1</t>
-  </si>
-  <si>
-    <t>питание кулера 1</t>
-  </si>
-  <si>
-    <t>AC</t>
-  </si>
-  <si>
-    <t>TMSPWRFAN2</t>
-  </si>
-  <si>
-    <t>питание кулера 2</t>
-  </si>
-  <si>
-    <t>TMSPWRFAN3</t>
-  </si>
-  <si>
-    <t>питание кулера 3</t>
-  </si>
-  <si>
-    <t>TMSPWRFAN4</t>
-  </si>
-  <si>
-    <t>питание кулера 4</t>
-  </si>
-  <si>
-    <t>TMST</t>
-  </si>
-  <si>
-    <t>температура TMS</t>
-  </si>
-  <si>
-    <t>MNSPWR</t>
-  </si>
-  <si>
-    <t>MNS</t>
-  </si>
-  <si>
-    <t>MNSCLOCK</t>
-  </si>
-  <si>
-    <t>счетчик MNS</t>
-  </si>
-  <si>
-    <t>MNST</t>
-  </si>
-  <si>
-    <t>температура MNS</t>
-  </si>
-  <si>
-    <t>LSPWR</t>
-  </si>
-  <si>
-    <t>LS вкл/выкл</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>LSCLOCK</t>
-  </si>
-  <si>
-    <t>счетчик LS</t>
-  </si>
-  <si>
-    <t>LST</t>
-  </si>
-  <si>
-    <t>температура LS</t>
-  </si>
-  <si>
-    <t>CPSSINIT</t>
-  </si>
-  <si>
-    <t>запуск PSS системы</t>
-  </si>
-  <si>
-    <t>CPSSPWRON</t>
-  </si>
-  <si>
-    <t>PSS вкл</t>
-  </si>
-  <si>
-    <t>CPSSPWROFF</t>
-  </si>
-  <si>
-    <t>PSS выкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR12ON</t>
-  </si>
-  <si>
-    <t>питание контура 12V вкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR12OFF</t>
-  </si>
-  <si>
-    <t>питание контура 12V выкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR6ON</t>
-  </si>
-  <si>
-    <t>питание контура 6V вкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR6OFF</t>
-  </si>
-  <si>
-    <t>питание контура 6V выкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR5ON</t>
-  </si>
-  <si>
-    <t>питание контура 5V вкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR5OFF</t>
-  </si>
-  <si>
-    <t>питание контура 5V выкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR33ON</t>
-  </si>
-  <si>
-    <t>питание контура 3.3V вкл</t>
-  </si>
-  <si>
-    <t>CPSSPWR33OFF</t>
-  </si>
-  <si>
-    <t>питание контура 3.3V выкл</t>
-  </si>
-  <si>
-    <t>CPSSECOON</t>
-  </si>
-  <si>
-    <t>режим экономии энергии вкл</t>
-  </si>
-  <si>
-    <t>CPSSECOOFF</t>
-  </si>
-  <si>
-    <t>режим экономии энергии выкл</t>
-  </si>
-  <si>
-    <t>CPSSMAXT1</t>
-  </si>
-  <si>
-    <t>CPSSMAXT2</t>
-  </si>
-  <si>
-    <t>CPSSMAXA</t>
-  </si>
-  <si>
-    <t>CPSSMAXW</t>
-  </si>
-  <si>
-    <t>CPSSMINC</t>
-  </si>
-  <si>
-    <t>CPSSMINV</t>
-  </si>
-  <si>
-    <t>CPSSMAXA12</t>
-  </si>
-  <si>
-    <t>CPSSMAXA6</t>
-  </si>
-  <si>
-    <t>CPSSMAXA5</t>
   </si>
   <si>
     <t>CPSSCLOCK</t>
@@ -1048,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1057,16 +1072,17 @@
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.85546875" customWidth="1"/>
     <col min="6" max="6" width="4.140625" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,1311 +1122,1407 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
       </c>
       <c r="L8">
         <v>8</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10">
         <v>32</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
       <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11">
         <v>48</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12">
         <v>56</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>8</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13">
         <v>64</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14">
         <v>72</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>8</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15">
         <v>80</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16">
         <v>88</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>8</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17">
         <v>96</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18">
         <v>104</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>8</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19">
         <v>112</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
       <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20">
         <v>128</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
       <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21">
         <v>144</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22">
         <v>152</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>8</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23">
         <v>160</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24">
         <v>168</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>8</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25">
         <v>176</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26">
         <v>184</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>8</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27">
         <v>192</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
       <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28">
         <v>200</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>8</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29">
         <v>208</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
       <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30">
         <v>216</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>8</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31">
         <v>224</v>
       </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
       <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32">
         <v>232</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>8</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2418,327 +2530,351 @@
       <c r="M33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>20</v>
       </c>
       <c r="L34">
         <v>1</v>
       </c>
       <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" t="s">
         <v>88</v>
       </c>
-      <c r="D35" t="s">
-        <v>84</v>
-      </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>20</v>
       </c>
       <c r="L35">
         <v>2</v>
       </c>
       <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>20</v>
       </c>
       <c r="L36">
         <v>3</v>
       </c>
       <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>3</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
       </c>
       <c r="L37">
         <v>4</v>
       </c>
       <c r="M37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>4</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
       </c>
       <c r="L38">
         <v>8</v>
       </c>
       <c r="M38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
         <v>34</v>
       </c>
-      <c r="F39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
-        <v>18</v>
-      </c>
-      <c r="K39">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>20</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G40" t="s">
+        <v>39</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40">
         <v>32</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
       <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>18</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>20</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2746,286 +2882,307 @@
       <c r="M41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>20</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
         <v>105</v>
       </c>
-      <c r="D43" t="s">
-        <v>101</v>
-      </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>-10</v>
-      </c>
-      <c r="J43" t="s">
-        <v>106</v>
-      </c>
-      <c r="K43">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>110</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>-10</v>
-      </c>
-      <c r="J44" t="s">
-        <v>106</v>
-      </c>
-      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44">
         <v>24</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>8</v>
       </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
         <v>110</v>
       </c>
-      <c r="D45" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>-10</v>
-      </c>
-      <c r="J45" t="s">
-        <v>106</v>
-      </c>
-      <c r="K45">
+      <c r="L45">
         <v>32</v>
       </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
       <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>-10</v>
-      </c>
-      <c r="J46" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>110</v>
+      </c>
+      <c r="L46">
         <v>40</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>8</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
-        <v>18</v>
-      </c>
-      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>20</v>
+      </c>
+      <c r="L47">
         <v>48</v>
       </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
       <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
-        <v>18</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>20</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -3033,122 +3190,131 @@
       <c r="M48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>18</v>
-      </c>
-      <c r="K49">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
+        <v>20</v>
       </c>
       <c r="L49">
         <v>8</v>
       </c>
       <c r="M49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" t="s">
         <v>120</v>
       </c>
-      <c r="D50" t="s">
-        <v>116</v>
-      </c>
       <c r="E50" t="s">
-        <v>34</v>
-      </c>
-      <c r="F50" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>18</v>
-      </c>
-      <c r="K50">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>20</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51" t="s">
-        <v>18</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>20</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -3156,86 +3322,95 @@
       <c r="M51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>34</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>18</v>
-      </c>
-      <c r="K52">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>20</v>
       </c>
       <c r="L52">
         <v>8</v>
       </c>
       <c r="M52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" t="s">
         <v>127</v>
       </c>
-      <c r="D53" t="s">
-        <v>123</v>
-      </c>
       <c r="E53" t="s">
-        <v>34</v>
-      </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>18</v>
-      </c>
-      <c r="K53">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>20</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
         <v>1</v>
       </c>
     </row>
@@ -3246,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E77D5F1-EDD8-4F0B-B692-783EE3CD41AF}">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3255,16 +3430,17 @@
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.85546875" customWidth="1"/>
     <col min="6" max="6" width="4.140625" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3304,1024 +3480,1099 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
       </c>
       <c r="L10">
         <v>8</v>
       </c>
       <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
       </c>
       <c r="L11">
         <v>9</v>
       </c>
       <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
       </c>
       <c r="L12">
         <v>10</v>
       </c>
       <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>20</v>
       </c>
       <c r="L13">
         <v>11</v>
       </c>
       <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>11</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>20</v>
       </c>
       <c r="L14">
         <v>12</v>
       </c>
       <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>12</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16">
         <v>32</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
       <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17">
         <v>48</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18">
         <v>56</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>8</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19">
         <v>64</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
       <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>39</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20">
         <v>72</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>8</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21">
         <v>80</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22">
         <v>88</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>8</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23">
         <v>96</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>39</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24">
         <v>104</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>8</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25">
         <v>112</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -4329,532 +4580,571 @@
       <c r="M26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
       </c>
       <c r="L27">
         <v>1</v>
       </c>
       <c r="M27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
       </c>
       <c r="L28">
         <v>2</v>
       </c>
       <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
       </c>
       <c r="L29">
         <v>3</v>
       </c>
       <c r="M29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>20</v>
       </c>
       <c r="L30">
         <v>4</v>
       </c>
       <c r="M30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>4</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
       </c>
       <c r="L31">
         <v>5</v>
       </c>
       <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>6</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
       </c>
       <c r="L33">
         <v>7</v>
       </c>
       <c r="M33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>7</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>20</v>
       </c>
       <c r="L34">
         <v>8</v>
       </c>
       <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>20</v>
       </c>
       <c r="L35">
         <v>9</v>
       </c>
       <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>20</v>
       </c>
       <c r="L36">
         <v>10</v>
       </c>
       <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>10</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
         <v>34</v>
       </c>
-      <c r="F37" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38">
         <v>32</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
       <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
-        <v>18</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>20</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4862,327 +5152,351 @@
       <c r="M39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C40" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>20</v>
       </c>
       <c r="L40">
         <v>1</v>
       </c>
       <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>18</v>
-      </c>
-      <c r="K41">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>20</v>
       </c>
       <c r="L41">
         <v>2</v>
       </c>
       <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>20</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
         <v>105</v>
       </c>
-      <c r="D43" t="s">
-        <v>101</v>
-      </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
         <v>-10</v>
       </c>
-      <c r="J43" t="s">
-        <v>106</v>
-      </c>
-      <c r="K43">
-        <v>16</v>
+      <c r="K43" t="s">
+        <v>110</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
         <v>-10</v>
       </c>
-      <c r="J44" t="s">
-        <v>106</v>
-      </c>
-      <c r="K44">
+      <c r="K44" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44">
         <v>24</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>8</v>
       </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>-10</v>
+      </c>
+      <c r="K45" t="s">
         <v>110</v>
       </c>
-      <c r="D45" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>-10</v>
-      </c>
-      <c r="J45" t="s">
-        <v>106</v>
-      </c>
-      <c r="K45">
+      <c r="L45">
         <v>32</v>
       </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
       <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
         <v>-10</v>
       </c>
-      <c r="J46" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46">
+      <c r="K46" t="s">
+        <v>110</v>
+      </c>
+      <c r="L46">
         <v>40</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>8</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
-        <v>18</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>20</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5190,163 +5504,175 @@
       <c r="M47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
-        <v>18</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>20</v>
       </c>
       <c r="L48">
         <v>1</v>
       </c>
       <c r="M48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>18</v>
-      </c>
-      <c r="K49">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
+        <v>20</v>
       </c>
       <c r="L49">
         <v>2</v>
       </c>
       <c r="M49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D50" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>34</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>18</v>
-      </c>
-      <c r="K50">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>20</v>
       </c>
       <c r="L50">
         <v>8</v>
       </c>
       <c r="M50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51" t="s">
-        <v>18</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>20</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5354,127 +5680,139 @@
       <c r="M51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C52" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>18</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>20</v>
       </c>
       <c r="L52">
         <v>1</v>
       </c>
       <c r="M52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C53" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D53" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>18</v>
-      </c>
-      <c r="K53">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>20</v>
       </c>
       <c r="L53">
         <v>2</v>
       </c>
       <c r="M53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D54" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>34</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>18</v>
-      </c>
-      <c r="K54">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>20</v>
       </c>
       <c r="L54">
         <v>8</v>
       </c>
       <c r="M54">
+        <v>8</v>
+      </c>
+      <c r="N54">
         <v>0</v>
       </c>
     </row>

--- a/software/data_base/BD.xlsx
+++ b/software/data_base/BD.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{226983AC-5BED-486D-8EAF-5E32545E1B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AEE16B7-99C3-44E3-961A-00DA7178BE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
     <sheet name="Commands" sheetId="2" r:id="rId2"/>
+    <sheet name="CS_Params" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="228">
   <si>
     <t>ID</t>
   </si>
@@ -695,6 +696,27 @@
   </si>
   <si>
     <t>задать счетчик LS</t>
+  </si>
+  <si>
+    <t>CSPWR</t>
+  </si>
+  <si>
+    <t>CS вкл/выкл</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CSCLOCK</t>
+  </si>
+  <si>
+    <t>счетчик CS</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>температура CS</t>
   </si>
 </sst>
 </file>
@@ -5819,4 +5841,115 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AAEEF3C-8ABB-4EC8-B7E6-4097F54F3917}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" customWidth="1"/>
+    <col min="6" max="6" width="4.140625" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>